--- a/branches/hiv-patient_fhir-182/ValueSet-vs-key-population-status.xlsx
+++ b/branches/hiv-patient_fhir-182/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/ValueSet-vs-key-population-status.xlsx
+++ b/branches/hiv-patient_fhir-182/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:11+00:00</t>
+    <t>2023-05-05T18:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/ValueSet-vs-key-population-status.xlsx
+++ b/branches/hiv-patient_fhir-182/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:45:12+00:00</t>
+    <t>2023-05-05T19:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/ValueSet-vs-key-population-status.xlsx
+++ b/branches/hiv-patient_fhir-182/ValueSet-vs-key-population-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
